--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:12</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Hualpén</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Lota</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:08</t>
+    <t xml:space="preserve">2026-10-04 08:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:55</t>
+    <t xml:space="preserve">2026-10-05 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -614,7 +614,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1279217.12</v>
+        <v>1279217.13</v>
       </c>
     </row>
     <row r="5">
@@ -682,7 +682,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1140871.12</v>
+        <v>1140871.13</v>
       </c>
     </row>
     <row r="9">
@@ -716,7 +716,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1127284.12</v>
+        <v>1127284.13</v>
       </c>
     </row>
     <row r="11">
@@ -1005,7 +1005,7 @@
         <v>2024</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>949321.12</v>
+        <v>949321.13</v>
       </c>
     </row>
     <row r="28">
@@ -1056,7 +1056,7 @@
         <v>2024</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>938161.62</v>
+        <v>938161.63</v>
       </c>
     </row>
     <row r="31">
